--- a/BVL-base-datos.xlsx
+++ b/BVL-base-datos.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Actualizado: 2026-07-09</t>
+          <t>Actualizado: 2026-07-20</t>
         </is>
       </c>
     </row>
@@ -518,11 +518,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3T2024</t>
+          <t>1T2021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -543,11 +543,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3T2024</t>
+          <t>1T2021</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1T2025</t>
+          <t>1T2021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3T2024</t>
+          <t>2T2022</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3467,6 +3467,1308 @@
       </c>
       <c r="W8" t="n">
         <v>872.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>462.37</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1726.13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="L9" t="n">
+        <v>685.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>888.51</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2024_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>11534.98</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3710.02</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7824.96</v>
+      </c>
+      <c r="V9" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>653.5599999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>545.22</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1839.56</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>777.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>878.96</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2024_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>11611.67</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4263.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7347.88</v>
+      </c>
+      <c r="V10" t="n">
+        <v>220.11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>670.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>477.86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2023.33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="L11" t="n">
+        <v>674.88</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1056</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2023_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>12355.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5411.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6943.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>660.78</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1010.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>531.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1793.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>800.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1080.22</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2023_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>10444.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3983.54</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6461.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>178.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1014.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>555.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1784.93</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>792.02</v>
+      </c>
+      <c r="M13" t="n">
+        <v>977.73</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2023_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>9553.459999999999</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3654.64</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5898.82</v>
+      </c>
+      <c r="V13" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1046.37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>537.36</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1792.13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="L14" t="n">
+        <v>821.9400000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>901.28</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2023_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>9503.58</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4137.82</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5365.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>162.56</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1407.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1917</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="L15" t="n">
+        <v>745.51</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1097.21</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2022_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>11388.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6398.63</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4989.52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>878.0599999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>416.66</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1643.31</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5275</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>724</v>
+      </c>
+      <c r="M16" t="n">
+        <v>982.26</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2022_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>9489.459999999999</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5005.97</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4483.49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>302.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1622.03</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="L17" t="n">
+        <v>601.6900000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>771.6900000000001</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2022_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>8803.440000000001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4773.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4029.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>128.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>366.38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>505.79</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1560.77</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="K18" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="L18" t="n">
+        <v>637.4400000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>717.01</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2022_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>8652.620000000001</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5022.23</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3630.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1061.89</v>
+      </c>
+      <c r="W18" t="n">
+        <v>493.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>553.91</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1835.74</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="K19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>768.26</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1117.43</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2021_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>8588.780000000001</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5252.47</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3336.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1039.98</v>
+      </c>
+      <c r="W19" t="n">
+        <v>600.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>417.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1483.63</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="L20" t="n">
+        <v>669.98</v>
+      </c>
+      <c r="M20" t="n">
+        <v>911.21</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2021_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>9151.280000000001</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3386.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5764.92</v>
+      </c>
+      <c r="V20" t="n">
+        <v>86.12</v>
+      </c>
+      <c r="W20" t="n">
+        <v>457.92</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>312.91</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1209.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L21" t="n">
+        <v>434.66</v>
+      </c>
+      <c r="M21" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2021_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>4887.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2432.54</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2454.79</v>
+      </c>
+      <c r="V21" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>710.38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UNION DE CERVECERIAS PERUANAS BACKUS Y JOHNSTON S.A.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>424.65</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1356.14</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="L22" t="n">
+        <v>584.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>656.78</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNION_DE_CERVECERIAS_PERUANAS_BACKUS_Y_J_2021_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>6025.74</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3935.78</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2089.95</v>
+      </c>
+      <c r="V22" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>597.4299999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3480,7 +4782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,6 +5551,1308 @@
       </c>
       <c r="W8" t="n">
         <v>139.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I9" t="n">
+        <v>457.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6034</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L9" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>157.2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2024_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>3218.01</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1941.81</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1276.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1539.17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>87.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>476.55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6138</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="L10" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2024_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>3209.13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1969.68</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1239.45</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1578.88</v>
+      </c>
+      <c r="W10" t="n">
+        <v>55.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>511.38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6306</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L11" t="n">
+        <v>117.16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>261.36</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2023_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>3221.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2031.73</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1190.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1581.15</v>
+      </c>
+      <c r="W11" t="n">
+        <v>90.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>516.66</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="L12" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>196.84</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2023_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>3404.03</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2074.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1329.69</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1580.77</v>
+      </c>
+      <c r="W12" t="n">
+        <v>177.12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>442.04</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L13" t="n">
+        <v>78.65000000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>146.56</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2023_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>3348.49</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2064.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1283.58</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1620.18</v>
+      </c>
+      <c r="W13" t="n">
+        <v>65.66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="I14" t="n">
+        <v>480</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6223</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L14" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2023_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>3283.64</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2043.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1240.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1616.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>45.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="I15" t="n">
+        <v>533.89</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L15" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2022_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>3314.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2119.03</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1195.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1597.53</v>
+      </c>
+      <c r="W15" t="n">
+        <v>81.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>553.5599999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="L16" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="M16" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2022_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>3372.06</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2037.19</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1334.87</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1544.95</v>
+      </c>
+      <c r="W16" t="n">
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>502.89</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="M17" t="n">
+        <v>154.42</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2022_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>3271.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1981.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1289.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1524.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>277.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="I18" t="n">
+        <v>525.41</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L18" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>127.47</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2022_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>3174.12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1931.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1242.97</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1504.78</v>
+      </c>
+      <c r="W18" t="n">
+        <v>264.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>524.87</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="L19" t="n">
+        <v>107.42</v>
+      </c>
+      <c r="M19" t="n">
+        <v>242.99</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2021_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>3201.77</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2005.97</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1195.81</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1551.18</v>
+      </c>
+      <c r="W19" t="n">
+        <v>273.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>507.17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.6365</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L20" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>184.97</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2021_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>3149.24</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2004.56</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1144.68</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1572.28</v>
+      </c>
+      <c r="W20" t="n">
+        <v>298.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="I21" t="n">
+        <v>440.92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L21" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="M21" t="n">
+        <v>123.81</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2021_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>3142.66</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2049.31</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1093.35</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1311.68</v>
+      </c>
+      <c r="W21" t="n">
+        <v>368.65</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CEMENTOS PACASMAYO S.A.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>464.81</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L22" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="M22" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CEMENTOS_PACASMAYO_S_A_A__2021_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>3080.47</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1676.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1403.51</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1295.55</v>
+      </c>
+      <c r="W22" t="n">
+        <v>305.31</v>
       </c>
     </row>
   </sheetData>
@@ -8472,7 +11076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9055,6 +11659,1494 @@
       </c>
       <c r="W6" t="n">
         <v>223.38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>134.56</v>
+      </c>
+      <c r="I7" t="n">
+        <v>420.91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="L7" t="n">
+        <v>197.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>219.36</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1235.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>714.1799999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>169.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>104.51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>143.16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>159.94</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1067.93</v>
+      </c>
+      <c r="T8" t="n">
+        <v>680.03</v>
+      </c>
+      <c r="U8" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W8" t="n">
+        <v>197.94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="I9" t="n">
+        <v>292.03</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6863</v>
+      </c>
+      <c r="K9" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>119.71</v>
+      </c>
+      <c r="M9" t="n">
+        <v>130.93</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>903.27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>619.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>283.39</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W9" t="n">
+        <v>194.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>256.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7862</v>
+      </c>
+      <c r="K10" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112.77</v>
+      </c>
+      <c r="M10" t="n">
+        <v>118.31</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>946.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>743.99</v>
+      </c>
+      <c r="U10" t="n">
+        <v>202.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W10" t="n">
+        <v>68.66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="L11" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>154.68</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>899.67</v>
+      </c>
+      <c r="T11" t="n">
+        <v>418.81</v>
+      </c>
+      <c r="U11" t="n">
+        <v>480.86</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>154.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="L12" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>766.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>153.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="I13" t="n">
+        <v>265.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>724.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>417.56</v>
+      </c>
+      <c r="U13" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W13" t="n">
+        <v>116.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>245.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="K14" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1509.03</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1301.97</v>
+      </c>
+      <c r="U14" t="n">
+        <v>207.06</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W14" t="n">
+        <v>122.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="I15" t="n">
+        <v>304.92</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>151.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>1350.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>854.4299999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>496.07</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="W15" t="n">
+        <v>161.43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="I16" t="n">
+        <v>299.52</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6588000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="L16" t="n">
+        <v>133.58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>153.26</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>1151.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>758.6799999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>89.92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>267.16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7131999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="L17" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>146.33</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>1029.86</v>
+      </c>
+      <c r="T17" t="n">
+        <v>734.46</v>
+      </c>
+      <c r="U17" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="W17" t="n">
+        <v>146.38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>82.31</v>
+      </c>
+      <c r="I18" t="n">
+        <v>221.09</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7837</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="L18" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="M18" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>912.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>715.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>197.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>61.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>119.73</v>
+      </c>
+      <c r="I19" t="n">
+        <v>296.47</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="K19" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="L19" t="n">
+        <v>165.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>192.25</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>871.41</v>
+      </c>
+      <c r="T19" t="n">
+        <v>388.49</v>
+      </c>
+      <c r="U19" t="n">
+        <v>482.92</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="W19" t="n">
+        <v>81.51000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>282.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5147</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="L20" t="n">
+        <v>117.19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>137.32</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>746.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>384.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>103.87</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I21" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="L21" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="M21" t="n">
+        <v>113.83</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>620.48</v>
+      </c>
+      <c r="T21" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="U21" t="n">
+        <v>277.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W21" t="n">
+        <v>178.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8132</v>
+      </c>
+      <c r="K22" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>1176.21</v>
+      </c>
+      <c r="T22" t="n">
+        <v>956.4400000000001</v>
+      </c>
+      <c r="U22" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="W22" t="n">
+        <v>123.7</v>
       </c>
     </row>
   </sheetData>
@@ -9068,7 +13160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9853,6 +13945,861 @@
         <v>367.21</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1666.94</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>242.84</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2024_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>13978.24</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8015.13</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5963.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5707.18</v>
+      </c>
+      <c r="W9" t="n">
+        <v>337.64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1605.41</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L10" t="n">
+        <v>272.81</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2024_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>13841</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7870.09</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5970.91</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5571.31</v>
+      </c>
+      <c r="W10" t="n">
+        <v>466.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1657.57</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5697</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L11" t="n">
+        <v>257.22</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2023_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>13714.89</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7812.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5901.99</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5498.54</v>
+      </c>
+      <c r="W11" t="n">
+        <v>401.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1749.82</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L12" t="n">
+        <v>224.57</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2023_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>12326.69</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6471.79</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5854.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4324.63</v>
+      </c>
+      <c r="W12" t="n">
+        <v>376.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>128.56</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1558.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L13" t="n">
+        <v>238.01</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2023_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>12019.83</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6222.36</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5797.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4243.47</v>
+      </c>
+      <c r="W13" t="n">
+        <v>323.56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>170.63</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1409.53</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L14" t="n">
+        <v>269.82</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2023_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>11565.97</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5774.02</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5791.95</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4053.39</v>
+      </c>
+      <c r="W14" t="n">
+        <v>447.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>194.58</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1604.48</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4998</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>260.07</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2022_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>11389.07</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5692.26</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5696.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3735.88</v>
+      </c>
+      <c r="W15" t="n">
+        <v>334.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>162.74</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1570.49</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L16" t="n">
+        <v>290.59</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2022_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>11371.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5731.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5640.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3803.39</v>
+      </c>
+      <c r="W16" t="n">
+        <v>376.21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UNACEM CORP S.A.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1429.57</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L17" t="n">
+        <v>236.83</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_UNACEM_CORP_S_A_A__2022_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>11045.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5560.41</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5485.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3811.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>356.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BVL-base-datos.xlsx
+++ b/BVL-base-datos.xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPACASC1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CVERDEC1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FERREYC1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNJUANC1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNACEMC1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUSURC1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNJUANC1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNACEMC1" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -609,20 +610,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SNJUANC1</t>
+          <t>LUSURC1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1T2021</t>
+          <t>3T2021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -634,23 +635,48 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>SNJUANC1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1T2021</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1T2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>UNACEMC1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>UNACEM CORP S.A.A.</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>16</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2T2022</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1T2026</t>
         </is>
@@ -11076,7 +11102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11199,7 +11225,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11231,22 +11257,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>160.83</v>
+        <v>218.76</v>
       </c>
       <c r="I2" t="n">
-        <v>313.68</v>
+        <v>1228.9</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8124</v>
+        <v>0.5579</v>
       </c>
       <c r="K2" t="n">
-        <v>58.09</v>
+        <v>3.87</v>
       </c>
       <c r="L2" t="n">
-        <v>149.58</v>
-      </c>
-      <c r="M2" t="n">
-        <v>154.29</v>
+        <v>369.85</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -11255,12 +11283,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -11270,29 +11298,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2026_TRIMESTREI.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2026_TRIMESTREI.xlsx</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1475.48</v>
+        <v>12796.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1198.62</v>
+        <v>7138.82</v>
       </c>
       <c r="U2" t="n">
-        <v>276.86</v>
+        <v>5658.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.65</v>
+        <v>4791.84</v>
       </c>
       <c r="W2" t="n">
-        <v>182.23</v>
+        <v>605.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11324,22 +11352,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>154.52</v>
+        <v>173.87</v>
       </c>
       <c r="I3" t="n">
-        <v>390.04</v>
+        <v>1216.86</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5288</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>24.09</v>
+        <v>3.16</v>
       </c>
       <c r="L3" t="n">
-        <v>188.12</v>
-      </c>
-      <c r="M3" t="n">
-        <v>210.08</v>
+        <v>305.27</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -11348,12 +11378,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -11363,29 +11393,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIV.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2025_TRIMESTREIV.xlsx</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1361.18</v>
+        <v>12531.75</v>
       </c>
       <c r="T3" t="n">
-        <v>719.77</v>
+        <v>7030.9</v>
       </c>
       <c r="U3" t="n">
-        <v>641.41</v>
+        <v>5500.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6899999999999999</v>
+        <v>4834.74</v>
       </c>
       <c r="W3" t="n">
-        <v>322.13</v>
+        <v>553.5599999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11417,22 +11447,24 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>169.55</v>
+        <v>181.1</v>
       </c>
       <c r="I4" t="n">
-        <v>359.26</v>
+        <v>1104.49</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.5617</v>
       </c>
       <c r="K4" t="n">
-        <v>34.77</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>185.49</v>
-      </c>
-      <c r="M4" t="n">
-        <v>202.46</v>
+        <v>297.09</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -11441,12 +11473,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -11456,29 +11488,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2025_TRIMESTREIII.xlsx</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1523.43</v>
+        <v>11177.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1035.81</v>
+        <v>6278.23</v>
       </c>
       <c r="U4" t="n">
-        <v>487.62</v>
+        <v>4899.37</v>
       </c>
       <c r="V4" t="n">
-        <v>0.83</v>
+        <v>4078.03</v>
       </c>
       <c r="W4" t="n">
-        <v>203.22</v>
+        <v>568.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11510,22 +11542,24 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>110.05</v>
+        <v>164.39</v>
       </c>
       <c r="I5" t="n">
-        <v>339.34</v>
+        <v>1140.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.761</v>
+        <v>0.5699</v>
       </c>
       <c r="K5" t="n">
-        <v>34.6</v>
+        <v>3.48</v>
       </c>
       <c r="L5" t="n">
-        <v>137.12</v>
-      </c>
-      <c r="M5" t="n">
-        <v>148.73</v>
+        <v>289.27</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -11534,12 +11568,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -11549,29 +11583,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2025_TRIMESTREII.xlsx</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1330.76</v>
+        <v>10998.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1012.7</v>
+        <v>6268.61</v>
       </c>
       <c r="U5" t="n">
-        <v>318.07</v>
+        <v>4729.95</v>
       </c>
       <c r="V5" t="n">
-        <v>0.96</v>
+        <v>4115.42</v>
       </c>
       <c r="W5" t="n">
-        <v>162.53</v>
+        <v>444.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11603,22 +11637,24 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>91.98999999999999</v>
+        <v>185.49</v>
       </c>
       <c r="I6" t="n">
-        <v>275.79</v>
+        <v>1206.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8455</v>
+        <v>0.591</v>
       </c>
       <c r="K6" t="n">
-        <v>44.22</v>
+        <v>4.07</v>
       </c>
       <c r="L6" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="M6" t="n">
-        <v>104.24</v>
+        <v>313.51</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -11627,12 +11663,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -11642,29 +11678,29 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREI.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2025_TRIMESTREI.xlsx</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1346.15</v>
+        <v>11153.37</v>
       </c>
       <c r="T6" t="n">
-        <v>1138.13</v>
+        <v>6591.21</v>
       </c>
       <c r="U6" t="n">
-        <v>208.02</v>
+        <v>4562.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8100000000000001</v>
+        <v>4424.41</v>
       </c>
       <c r="W6" t="n">
-        <v>223.38</v>
+        <v>553.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11696,22 +11732,24 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>134.56</v>
+        <v>151.39</v>
       </c>
       <c r="I7" t="n">
-        <v>420.91</v>
+        <v>1177.56</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="K7" t="n">
-        <v>25.82</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>197.22</v>
-      </c>
-      <c r="M7" t="n">
-        <v>219.36</v>
+        <v>298.94</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -11720,7 +11758,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -11735,29 +11773,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIV.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2024_TRIMESTREIV.xlsx</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1235.31</v>
+        <v>11259.93</v>
       </c>
       <c r="T7" t="n">
-        <v>714.1799999999999</v>
+        <v>6665.67</v>
       </c>
       <c r="U7" t="n">
-        <v>521.13</v>
+        <v>4594.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0.85</v>
+        <v>4480.21</v>
       </c>
       <c r="W7" t="n">
-        <v>169.36</v>
+        <v>633.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11789,22 +11827,24 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>104.51</v>
+        <v>194.81</v>
       </c>
       <c r="I8" t="n">
-        <v>342.55</v>
+        <v>1142.29</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6368</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>26.94</v>
+        <v>4.64</v>
       </c>
       <c r="L8" t="n">
-        <v>143.16</v>
-      </c>
-      <c r="M8" t="n">
-        <v>159.94</v>
+        <v>319.01</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -11813,7 +11853,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -11828,29 +11868,29 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2024_TRIMESTREIII.xlsx</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1067.93</v>
+        <v>10306.33</v>
       </c>
       <c r="T8" t="n">
-        <v>680.03</v>
+        <v>6103.44</v>
       </c>
       <c r="U8" t="n">
-        <v>387.9</v>
+        <v>4202.89</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>4371.06</v>
       </c>
       <c r="W8" t="n">
-        <v>197.94</v>
+        <v>343.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11882,22 +11922,24 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>81.03</v>
+        <v>172.17</v>
       </c>
       <c r="I9" t="n">
-        <v>292.03</v>
+        <v>1133.86</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6863</v>
+        <v>0.6091</v>
       </c>
       <c r="K9" t="n">
-        <v>28.59</v>
+        <v>4.27</v>
       </c>
       <c r="L9" t="n">
-        <v>119.71</v>
-      </c>
-      <c r="M9" t="n">
-        <v>130.93</v>
+        <v>317.83</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -11906,7 +11948,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -11921,29 +11963,29 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2024_TRIMESTREII.xlsx</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>903.27</v>
+        <v>10305.86</v>
       </c>
       <c r="T9" t="n">
-        <v>619.88</v>
+        <v>6277.14</v>
       </c>
       <c r="U9" t="n">
-        <v>283.39</v>
+        <v>4028.72</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>4490.28</v>
       </c>
       <c r="W9" t="n">
-        <v>194.43</v>
+        <v>285.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11975,22 +12017,24 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>86.33</v>
+        <v>196.28</v>
       </c>
       <c r="I10" t="n">
-        <v>256.75</v>
+        <v>1196.46</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7862</v>
+        <v>0.5558</v>
       </c>
       <c r="K10" t="n">
-        <v>42.66</v>
+        <v>5.09</v>
       </c>
       <c r="L10" t="n">
-        <v>112.77</v>
-      </c>
-      <c r="M10" t="n">
-        <v>118.31</v>
+        <v>331.62</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -11999,7 +12043,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -12014,29 +12058,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREI.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2024_TRIMESTREI.xlsx</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>946.36</v>
+        <v>8687.93</v>
       </c>
       <c r="T10" t="n">
-        <v>743.99</v>
+        <v>4828.58</v>
       </c>
       <c r="U10" t="n">
-        <v>202.37</v>
+        <v>3859.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0.27</v>
+        <v>3111.53</v>
       </c>
       <c r="W10" t="n">
-        <v>68.66</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12068,22 +12112,24 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94.29000000000001</v>
+        <v>160.03</v>
       </c>
       <c r="I11" t="n">
-        <v>316.64</v>
+        <v>1093.53</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4655</v>
+        <v>0.5632</v>
       </c>
       <c r="K11" t="n">
-        <v>19.61</v>
+        <v>4.17</v>
       </c>
       <c r="L11" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="M11" t="n">
-        <v>154.68</v>
+        <v>272.6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -12092,7 +12138,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -12107,29 +12153,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIV.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2023_TRIMESTREIV.xlsx</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>899.67</v>
+        <v>8784.059999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>418.81</v>
+        <v>4946.82</v>
       </c>
       <c r="U11" t="n">
-        <v>480.86</v>
+        <v>3837.24</v>
       </c>
       <c r="V11" t="n">
-        <v>0.36</v>
+        <v>3421.99</v>
       </c>
       <c r="W11" t="n">
-        <v>154.87</v>
+        <v>319.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12161,22 +12207,24 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>79.34999999999999</v>
+        <v>147.01</v>
       </c>
       <c r="I12" t="n">
-        <v>302.8</v>
+        <v>1091.05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4962</v>
+        <v>0.5209</v>
       </c>
       <c r="K12" t="n">
-        <v>20.54</v>
+        <v>3.79</v>
       </c>
       <c r="L12" t="n">
-        <v>122.37</v>
-      </c>
-      <c r="M12" t="n">
-        <v>140.9</v>
+        <v>250.49</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -12185,7 +12233,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -12200,29 +12248,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2023_TRIMESTREIII.xlsx</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>766.62</v>
+        <v>8090.56</v>
       </c>
       <c r="T12" t="n">
-        <v>380.38</v>
+        <v>4214.26</v>
       </c>
       <c r="U12" t="n">
-        <v>386.25</v>
+        <v>3876.3</v>
       </c>
       <c r="V12" t="n">
-        <v>2.29</v>
+        <v>2793.3</v>
       </c>
       <c r="W12" t="n">
-        <v>153.93</v>
+        <v>197.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -12254,22 +12302,24 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>99.84</v>
+        <v>203.47</v>
       </c>
       <c r="I13" t="n">
-        <v>265.75</v>
+        <v>1123.32</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5764</v>
+        <v>0.5083</v>
       </c>
       <c r="K13" t="n">
-        <v>32.53</v>
+        <v>5.22</v>
       </c>
       <c r="L13" t="n">
-        <v>135.32</v>
-      </c>
-      <c r="M13" t="n">
-        <v>147.75</v>
+        <v>325.38</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -12278,7 +12328,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -12293,29 +12343,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2023_TRIMESTREII.xlsx</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>724.46</v>
+        <v>7934.27</v>
       </c>
       <c r="T13" t="n">
-        <v>417.56</v>
+        <v>4033.09</v>
       </c>
       <c r="U13" t="n">
-        <v>306.9</v>
+        <v>3901.18</v>
       </c>
       <c r="V13" t="n">
-        <v>2.46</v>
+        <v>2606.5</v>
       </c>
       <c r="W13" t="n">
-        <v>116.55</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12347,22 +12397,24 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>91.34999999999999</v>
+        <v>231.61</v>
       </c>
       <c r="I14" t="n">
-        <v>245.38</v>
+        <v>1176.55</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8628</v>
+        <v>0.535</v>
       </c>
       <c r="K14" t="n">
-        <v>44.12</v>
+        <v>6.26</v>
       </c>
       <c r="L14" t="n">
-        <v>104.09</v>
-      </c>
-      <c r="M14" t="n">
-        <v>110.36</v>
+        <v>366.04</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -12371,7 +12423,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -12386,29 +12438,29 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREI.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2023_TRIMESTREI.xlsx</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1509.03</v>
+        <v>7951.48</v>
       </c>
       <c r="T14" t="n">
-        <v>1301.97</v>
+        <v>4253.77</v>
       </c>
       <c r="U14" t="n">
-        <v>207.06</v>
+        <v>3697.71</v>
       </c>
       <c r="V14" t="n">
-        <v>2.71</v>
+        <v>2571.8</v>
       </c>
       <c r="W14" t="n">
-        <v>122.13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -12440,22 +12492,24 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>101.33</v>
+        <v>174.31</v>
       </c>
       <c r="I15" t="n">
-        <v>304.92</v>
+        <v>1085.01</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6327</v>
+        <v>0.537</v>
       </c>
       <c r="K15" t="n">
-        <v>20.43</v>
+        <v>4.79</v>
       </c>
       <c r="L15" t="n">
-        <v>151.19</v>
-      </c>
-      <c r="M15" t="n">
-        <v>177.58</v>
+        <v>292.55</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -12464,7 +12518,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -12479,29 +12533,29 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIV.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2022_TRIMESTREIV.xlsx</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>1350.5</v>
+        <v>7852.8</v>
       </c>
       <c r="T15" t="n">
-        <v>854.4299999999999</v>
+        <v>4216.76</v>
       </c>
       <c r="U15" t="n">
-        <v>496.07</v>
+        <v>3636.04</v>
       </c>
       <c r="V15" t="n">
-        <v>2.96</v>
+        <v>2744.32</v>
       </c>
       <c r="W15" t="n">
-        <v>161.43</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -12533,22 +12587,24 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>97.53</v>
+        <v>167.3</v>
       </c>
       <c r="I16" t="n">
-        <v>299.52</v>
+        <v>1005.39</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.4968</v>
       </c>
       <c r="K16" t="n">
-        <v>24.82</v>
+        <v>4.27</v>
       </c>
       <c r="L16" t="n">
-        <v>133.58</v>
-      </c>
-      <c r="M16" t="n">
-        <v>153.26</v>
+        <v>269.34</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -12557,7 +12613,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -12572,29 +12628,29 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2022_TRIMESTREIII.xlsx</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1151.62</v>
+        <v>7778.51</v>
       </c>
       <c r="T16" t="n">
-        <v>758.6799999999999</v>
+        <v>3864.52</v>
       </c>
       <c r="U16" t="n">
-        <v>392.94</v>
+        <v>3913.99</v>
       </c>
       <c r="V16" t="n">
-        <v>3.46</v>
+        <v>2468.5</v>
       </c>
       <c r="W16" t="n">
-        <v>89.92</v>
+        <v>121.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -12626,22 +12682,24 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>97.98</v>
+        <v>167.02</v>
       </c>
       <c r="I17" t="n">
-        <v>267.16</v>
+        <v>948.6900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.5134</v>
       </c>
       <c r="K17" t="n">
-        <v>33.17</v>
+        <v>4.46</v>
       </c>
       <c r="L17" t="n">
-        <v>133.15</v>
-      </c>
-      <c r="M17" t="n">
-        <v>146.33</v>
+        <v>259.22</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -12650,7 +12708,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -12665,29 +12723,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREII.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2022_TRIMESTREII.xlsx</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>1029.86</v>
+        <v>7699.15</v>
       </c>
       <c r="T17" t="n">
-        <v>734.46</v>
+        <v>3952.47</v>
       </c>
       <c r="U17" t="n">
-        <v>295.4</v>
+        <v>3746.69</v>
       </c>
       <c r="V17" t="n">
-        <v>3.74</v>
+        <v>2580</v>
       </c>
       <c r="W17" t="n">
-        <v>146.38</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -12702,11 +12760,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TRIMESTRE I</t>
+          <t>TRIMESTRE IV</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -12719,22 +12777,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>82.31</v>
+        <v>153.94</v>
       </c>
       <c r="I18" t="n">
-        <v>221.09</v>
+        <v>918.36</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7837</v>
+        <v>0.5351</v>
       </c>
       <c r="K18" t="n">
-        <v>41.69</v>
+        <v>4.36</v>
       </c>
       <c r="L18" t="n">
-        <v>103.65</v>
-      </c>
-      <c r="M18" t="n">
-        <v>110.24</v>
+        <v>250.69</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -12743,7 +12803,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -12758,29 +12818,29 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREI.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2021_TRIMESTREIV.xlsx</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>912.52</v>
+        <v>7602.17</v>
       </c>
       <c r="T18" t="n">
-        <v>715.11</v>
+        <v>4068.01</v>
       </c>
       <c r="U18" t="n">
-        <v>197.42</v>
+        <v>3534.16</v>
       </c>
       <c r="V18" t="n">
-        <v>4.08</v>
+        <v>2708.8</v>
       </c>
       <c r="W18" t="n">
-        <v>61.56</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
+          <t>LUZ DEL SUR S.A.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12795,7 +12855,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TRIMESTRE IV</t>
+          <t>TRIMESTRE III</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -12812,22 +12872,24 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>119.73</v>
+        <v>155.34</v>
       </c>
       <c r="I19" t="n">
-        <v>296.47</v>
+        <v>859.6900000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4458</v>
+        <v>0.5367</v>
       </c>
       <c r="K19" t="n">
-        <v>24.79</v>
+        <v>4.43</v>
       </c>
       <c r="L19" t="n">
-        <v>165.07</v>
-      </c>
-      <c r="M19" t="n">
-        <v>192.25</v>
+        <v>239.52</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -12836,7 +12898,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA N/D: EEFF SMV con flujo por método directo, sin línea de D&amp;A. EEFF Consolidada.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -12851,302 +12913,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIV.xlsx</t>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_LUZ_DEL_SUR_S_A_A__2021_TRIMESTREIII.xlsx</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>871.41</v>
+        <v>7571.29</v>
       </c>
       <c r="T19" t="n">
-        <v>388.49</v>
+        <v>4063.5</v>
       </c>
       <c r="U19" t="n">
-        <v>482.92</v>
+        <v>3507.79</v>
       </c>
       <c r="V19" t="n">
-        <v>4.43</v>
+        <v>2724.84</v>
       </c>
       <c r="W19" t="n">
-        <v>81.51000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Perú</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BVL (Bolsa de Valores de Lima)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TRIMESTRE III</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SMV — Superintendencia del Mercado de Valores</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>84.95999999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>282.36</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5147</v>
-      </c>
-      <c r="K20" t="n">
-        <v>23.46</v>
-      </c>
-      <c r="L20" t="n">
-        <v>117.19</v>
-      </c>
-      <c r="M20" t="n">
-        <v>137.32</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Consolidada</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIII.xlsx</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>746.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>384.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>362.18</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>103.87</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Perú</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BVL (Bolsa de Valores de Lima)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TRIMESTRE II</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SMV — Superintendencia del Mercado de Valores</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>57.44</v>
-      </c>
-      <c r="I21" t="n">
-        <v>219.66</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.5532</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="L21" t="n">
-        <v>99.28</v>
-      </c>
-      <c r="M21" t="n">
-        <v>113.83</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Consolidada</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREII.xlsx</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>620.48</v>
-      </c>
-      <c r="T21" t="n">
-        <v>343.26</v>
-      </c>
-      <c r="U21" t="n">
-        <v>277.22</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W21" t="n">
-        <v>178.48</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CERVECERIA SAN JUAN S.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Perú</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BVL (Bolsa de Valores de Lima)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TRIMESTRE I</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SMV — Superintendencia del Mercado de Valores</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>208.25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8132</v>
-      </c>
-      <c r="K22" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="L22" t="n">
-        <v>85.29000000000001</v>
-      </c>
-      <c r="M22" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Consolidada</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREI.xlsx</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>1176.21</v>
-      </c>
-      <c r="T22" t="n">
-        <v>956.4400000000001</v>
-      </c>
-      <c r="U22" t="n">
-        <v>219.77</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="W22" t="n">
-        <v>123.7</v>
+        <v>189.67</v>
       </c>
     </row>
   </sheetData>
@@ -13160,6 +12943,2090 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:W22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bolsa de valores</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Trimestre</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fuente del balance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>URL del documento</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro del trimestre (M PEN)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Volumen de ventas (M PEN)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Nivel de endeudamiento (Pasivos/Activos)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROE trimestral (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>EBIT (M PEN)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>EBITDA (M PEN)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notas metodológicas</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_corrida</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_eeff</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>archivo_local</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>activos_M</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pasivos_M</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>patrimonio_M</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>deuda_financiera_M</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>caja_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>313.68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8124</v>
+      </c>
+      <c r="K2" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="L2" t="n">
+        <v>149.58</v>
+      </c>
+      <c r="M2" t="n">
+        <v>154.29</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2026_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1475.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1198.62</v>
+      </c>
+      <c r="U2" t="n">
+        <v>276.86</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="W2" t="n">
+        <v>182.23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="I3" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5288</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="L3" t="n">
+        <v>188.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>210.08</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1361.18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>719.77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>641.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>322.13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1523.43</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1035.81</v>
+      </c>
+      <c r="U4" t="n">
+        <v>487.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="W4" t="n">
+        <v>203.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="K5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>137.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>148.73</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1330.76</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1012.7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="W5" t="n">
+        <v>162.53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>275.79</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="M6" t="n">
+        <v>104.24</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1346.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1138.13</v>
+      </c>
+      <c r="U6" t="n">
+        <v>208.02</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>223.38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>134.56</v>
+      </c>
+      <c r="I7" t="n">
+        <v>420.91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="L7" t="n">
+        <v>197.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>219.36</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1235.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>714.1799999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>169.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>104.51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>143.16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>159.94</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1067.93</v>
+      </c>
+      <c r="T8" t="n">
+        <v>680.03</v>
+      </c>
+      <c r="U8" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W8" t="n">
+        <v>197.94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="I9" t="n">
+        <v>292.03</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6863</v>
+      </c>
+      <c r="K9" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>119.71</v>
+      </c>
+      <c r="M9" t="n">
+        <v>130.93</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>903.27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>619.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>283.39</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W9" t="n">
+        <v>194.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>256.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7862</v>
+      </c>
+      <c r="K10" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112.77</v>
+      </c>
+      <c r="M10" t="n">
+        <v>118.31</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2024_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>946.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>743.99</v>
+      </c>
+      <c r="U10" t="n">
+        <v>202.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W10" t="n">
+        <v>68.66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>316.64</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="L11" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>154.68</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>899.67</v>
+      </c>
+      <c r="T11" t="n">
+        <v>418.81</v>
+      </c>
+      <c r="U11" t="n">
+        <v>480.86</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>154.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="L12" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>766.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>153.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="I13" t="n">
+        <v>265.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>135.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>724.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>417.56</v>
+      </c>
+      <c r="U13" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W13" t="n">
+        <v>116.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>245.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="K14" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2023_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1509.03</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1301.97</v>
+      </c>
+      <c r="U14" t="n">
+        <v>207.06</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W14" t="n">
+        <v>122.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="I15" t="n">
+        <v>304.92</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>151.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>1350.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>854.4299999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>496.07</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="W15" t="n">
+        <v>161.43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="I16" t="n">
+        <v>299.52</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6588000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="L16" t="n">
+        <v>133.58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>153.26</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>1151.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>758.6799999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>89.92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>267.16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7131999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="L17" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>146.33</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>1029.86</v>
+      </c>
+      <c r="T17" t="n">
+        <v>734.46</v>
+      </c>
+      <c r="U17" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="W17" t="n">
+        <v>146.38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>82.31</v>
+      </c>
+      <c r="I18" t="n">
+        <v>221.09</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7837</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="L18" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="M18" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2022_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>912.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>715.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>197.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>61.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>119.73</v>
+      </c>
+      <c r="I19" t="n">
+        <v>296.47</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="K19" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="L19" t="n">
+        <v>165.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>192.25</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>871.41</v>
+      </c>
+      <c r="T19" t="n">
+        <v>388.49</v>
+      </c>
+      <c r="U19" t="n">
+        <v>482.92</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="W19" t="n">
+        <v>81.51000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>282.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5147</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="L20" t="n">
+        <v>117.19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>137.32</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>746.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>384.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>103.87</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I21" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="L21" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="M21" t="n">
+        <v>113.83</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>620.48</v>
+      </c>
+      <c r="T21" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="U21" t="n">
+        <v>277.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W21" t="n">
+        <v>178.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8132</v>
+      </c>
+      <c r="K22" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2021_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>1176.21</v>
+      </c>
+      <c r="T22" t="n">
+        <v>956.4400000000001</v>
+      </c>
+      <c r="U22" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="W22" t="n">
+        <v>123.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
